--- a/docs/PRAP_Development_Plan_v2.59.xlsx
+++ b/docs/PRAP_Development_Plan_v2.59.xlsx
@@ -7418,7 +7418,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>R-48, V-36: A PROJECT WITH NOBODY ON IT NOW SAYS WHAT IT NEEDS. Reported from the field: a project is added, and the application shows no FTE for it until somebody is assigned - even though the figure is computable from the moment its periods exist. IT WAS A SILENCE, NOT A WRONG NUMBER, WHICH IS WHY NOTHING CAUGHT IT. Until the first assignment the project had no row in Resource by project, no band on either chart and no share of any tile - while STILL being drawn on the timeline, which reads the project's own dates. So the screen said the project exists and when it runs, and then declined to say what it costs. Type, phase, scope and periods are all the standard needs; nothing was missing but the asking. AND THE RULE THAT SHOULD HAVE CAUGHT IT STRUCTURALLY COULD NOT. V-34 compares DEMAND against APPLIED, and a project staffed at nothing is that gap at its widest - but V-34 is built from projGap, which is built from projMonth, which is built from the LINES, and the lines come from the assignments. No assignment, no line, no entry, no finding. The one project short by the whole of its standard was the only shortfall the shortfall rule could not see. Measured on a fixture: a project needing 38.05 FTE-months produced ZERO calculated rows and ZERO findings in both the browser and tools/prap_io.py. V-36 IS INFORMATION AND CLASSED INCOMPLETE, and both were chosen rather than defaulted. A project with nobody on it yet is not a fault - it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52, and the same argument) - so it must never refuse an edit, never block a save and never ask a question. INCOMPLETE is the class for a row still being built whose finding answers itself, and this one answers itself the moment anybody is assigned. IT CARRIES THE FIGURE, and that is the whole point of raising it from the CALCULATION rather than from the validation. 'PRJ-099 has no assignments' tells a planner what they can already see; 'it needs 38.05 FTE-months over 24 months, peaking at 1.86 in 2026-10' tells them what it will cost to fix. Every term is the one an assignment with blank dates would get (REQ-CAL-15), so the figure is not an estimate OF the application's answer - it IS the application's answer, arrived at early. tools/test_unstaffed.py asserts exactly that in both directions: the total, the span, the peak and the peak month it predicts all equal the project's own once one assignment exists, and the finding then disappears. WHAT IT DELIBERATELY DOES NOT DO. It does not put the project in Resource by project or on the charts. That was the larger option and it was not the one chosen: the demand would have to become a property of the project-month rather than of the assignments, which is a better answer to the original complaint and a much wider change - it also breaks the stated invariant that the project and person tables reconcile, unless demand and applied are kept as separate figures. Recorded here so the option is not lost: the rule reports the number, the dashboard still does not show it. TWO OF MY OWN MISTAKES, BOTH CAUGHT BY THE PROJECT'S OWN CONVENTIONS RATHER THAN BY TESTING HARDER. The severity was written as 'info' where this application's vocabulary is fatal / error / warning / INFORMATION - it would have sorted and filtered wrongly everywhere, including in the suite that checks findings. And the reference implementation named months one later than the browser, because every other call in prap_io.py converts the 1-based month with month_key(y, m - 1) and the two new ones did not. The second was found only by running both engines on the same fixture and reading the two messages side by side, which is what the four-implementation rule is for.</t>
+          <t>R-48, V-36: A PROJECT WITH NOBODY ON IT NOW SAYS WHAT IT NEEDS. Reported from the field: a project is added, and the application shows no FTE for it until somebody is assigned - even though the figure is computable from the moment its periods exist. IT WAS A ROW OF BLANKS, NOT A WRONG NUMBER, WHICH IS WHY NOTHING CAUGHT IT. And the first wording of this entry got the symptom wrong: it said the project was absent from everything but the timeline. It is not. SCREENSHOTS SETTLED IT - the project IS listed in Resource by project, IS drawn on the timeline and IS counted in the projects tile. What it has is every month EMPTY, nothing on the three demand charts, no legend entry and no line in Standard vs staffed. That is worse than being absent, and it is the very failure V-34 exists for: a row of blanks reads as a project that costs nothing, exactly as a study needing 10.00 and staffed at 5.00 read as a study that only ever needed 5.00. Type, phase, scope and periods are all the standard needs; nothing was missing but the asking. AND THE RULE THAT SHOULD HAVE CAUGHT IT STRUCTURALLY COULD NOT. V-34 compares DEMAND against APPLIED, and a project staffed at nothing is that gap at its widest - but V-34 is built from projGap, which is built from projMonth, which is built from the LINES, and the lines come from the assignments. No assignment, no line, no entry, no finding. The one project short by the whole of its standard was the only shortfall the shortfall rule could not see. Measured on a fixture: a project needing 38.05 FTE-months produced ZERO calculated rows and ZERO findings in both the browser and tools/prap_io.py. V-36 IS INFORMATION AND CLASSED INCOMPLETE, and both were chosen rather than defaulted. A project with nobody on it yet is not a fault - it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52, and the same argument) - so it must never refuse an edit, never block a save and never ask a question. INCOMPLETE is the class for a row still being built whose finding answers itself, and this one answers itself the moment anybody is assigned. IT CARRIES THE FIGURE, and that is the whole point of raising it from the CALCULATION rather than from the validation. 'PRJ-099 has no assignments' tells a planner what they can already see; 'it needs 38.05 FTE-months over 24 months, peaking at 1.86 in 2026-10' tells them what it will cost to fix. Every term is the one an assignment with blank dates would get (REQ-CAL-15), so the figure is not an estimate OF the application's answer - it IS the application's answer, arrived at early. tools/test_unstaffed.py asserts exactly that in both directions: the total, the span, the peak and the peak month it predicts all equal the project's own once one assignment exists, and the finding then disappears. WHAT IT DELIBERATELY DOES NOT DO. It does not put the project in Resource by project or on the charts. That was the larger option and it was not the one chosen: the demand would have to become a property of the project-month rather than of the assignments, which is a better answer to the original complaint and a much wider change - it also breaks the stated invariant that the project and person tables reconcile, unless demand and applied are kept as separate figures. Recorded here so the option is not lost: the rule reports the number, the dashboard still does not show it. TWO OF MY OWN MISTAKES, BOTH CAUGHT BY THE PROJECT'S OWN CONVENTIONS RATHER THAN BY TESTING HARDER. The severity was written as 'info' where this application's vocabulary is fatal / error / warning / INFORMATION - it would have sorted and filtered wrongly everywhere, including in the suite that checks findings. And the reference implementation named months one later than the browser, because every other call in prap_io.py converts the 1-based month with month_key(y, m - 1) and the two new ones did not. The second was found only by running both engines on the same fixture and reading the two messages side by side, which is what the four-implementation rule is for.</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -16064,7 +16064,7 @@
       </c>
       <c r="C164" s="18" t="inlineStr">
         <is>
-          <t>Information - and classed INCOMPLETE, so it never refuses an edit and never questions a save. A project with nobody on it yet is not a fault: it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52). WHAT IT FIXES IS AN ABSENCE, NOT AN ERROR. Until the first assignment exists the application showed NOTHING for the project - no row in Resource by project, no band on either chart, no contribution to any tile - while still drawing it on the timeline, which reads the project's own dates. So the screen said the project exists and when it runs, and then declined to say what it costs, although type, phase, scope and periods are all the standard needs to say so. REQ-CAL-19 is explicit that the project-month IS its standard and the people on it DIVIDE it; a divisor of nobody does not make the demand nought. AND NOTHING ELSE REPORTED IT: V-34 compares demand against applied, which is this gap at its widest, but V-34 is built from projGap, which is built from projMonth, which is built from the LINES - so no assignment means no line, no entry and no finding, and the one project short by the whole of its standard was the only shortfall the shortfall rule could not see. IT CARRIES THE FIGURE, which is why it is raised from the calculation rather than from the validation, and why every term is the one an assignment with blank dates would get (REQ-CAL-15): the number it states is to the hundredth the number the project shows the moment somebody is assigned, which tools/test_unstaffed.py asserts in both directions. SKIPPED where there is nothing to say or nothing to do: a project with no periods has no demand to state and V-12 or V-16 already says so, and a Completed project is history rather than a gap to fill - its finding would never answer itself, which is what the INCOMPLETE class promises.</t>
+          <t>Information - and classed INCOMPLETE, so it never refuses an edit and never questions a save. A project with nobody on it yet is not a fault: it is the state every project is in for the minute after it is created, exactly as a person with no assignment is (v2.52). WHAT IT FIXES IS A ROW OF BLANKS, NOT AN ERROR. The project IS listed - it has a row in Resource by project, it is drawn on the timeline, and it counts in the projects tile - but every one of its months is EMPTY, it puts nothing on the three demand charts, it takes no legend entry and it reaches no line of Standard vs staffed. That is worse than being absent: a row of blanks reads as a project that costs nothing rather than one nobody has been put on yet, which is the same failure V-34 exists for. Type, phase, scope and periods are all the standard needs to say what it costs. REQ-CAL-19 is explicit that the project-month IS its standard and the people on it DIVIDE it; a divisor of nobody does not make the demand nought. AND NOTHING ELSE REPORTED IT: V-34 compares demand against applied, which is this gap at its widest, but V-34 is built from projGap, which is built from projMonth, which is built from the LINES - so no assignment means no line, no entry and no finding, and the one project short by the whole of its standard was the only shortfall the shortfall rule could not see. IT CARRIES THE FIGURE, which is why it is raised from the calculation rather than from the validation, and why every term is the one an assignment with blank dates would get (REQ-CAL-15): the number it states is to the hundredth the number the project shows the moment somebody is assigned, which tools/test_unstaffed.py asserts in both directions. SKIPPED where there is nothing to say or nothing to do: a project with no periods has no demand to state and V-12 or V-16 already says so, and a Completed project is history rather than a gap to fill - its finding would never answer itself, which is what the INCOMPLETE class promises.</t>
         </is>
       </c>
     </row>
